--- a/artfynd/A 42749-2026 artfynd.xlsx
+++ b/artfynd/A 42749-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -981,6 +981,127 @@
       <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119101237</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137282906</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79503</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sadjem, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>771615</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7441266</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137282906</t>
         </is>
       </c>
     </row>
@@ -989,6 +1110,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42749-2026 artfynd.xlsx
+++ b/artfynd/A 42749-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>137282906</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42749-2026 artfynd.xlsx
+++ b/artfynd/A 42749-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>137282906</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42749-2026 artfynd.xlsx
+++ b/artfynd/A 42749-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>137282906</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42749-2026 artfynd.xlsx
+++ b/artfynd/A 42749-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>137282906</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42749-2026 artfynd.xlsx
+++ b/artfynd/A 42749-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>137282906</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42749-2026 artfynd.xlsx
+++ b/artfynd/A 42749-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>137282906</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 42749-2026 artfynd.xlsx
+++ b/artfynd/A 42749-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>137282906</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
